--- a/artfynd/A 57763-2024 artfynd.xlsx
+++ b/artfynd/A 57763-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114560357</v>
+        <v>114563174</v>
       </c>
       <c r="B2" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +708,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352055</v>
+        <v>352066</v>
       </c>
       <c r="R2" t="n">
-        <v>6422379</v>
+        <v>6422381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,37 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114563174</v>
+        <v>114560488</v>
       </c>
       <c r="B3" t="n">
-        <v>56178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,26 +829,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352066</v>
+        <v>352075</v>
       </c>
       <c r="R3" t="n">
-        <v>6422381</v>
+        <v>6422382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,47 +897,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114560358</v>
+        <v>114560489</v>
       </c>
       <c r="B4" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>352031</v>
+        <v>352096</v>
       </c>
       <c r="R4" t="n">
-        <v>6422314</v>
+        <v>6422425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,52 +1003,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114563201</v>
+        <v>114560405</v>
       </c>
       <c r="B5" t="n">
-        <v>56183</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1077,7 +1047,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352058</v>
+        <v>352088</v>
       </c>
       <c r="R5" t="n">
         <v>6422365</v>
@@ -1107,22 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,52 +1109,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114563197</v>
+        <v>114560406</v>
       </c>
       <c r="B6" t="n">
-        <v>56183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1203,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352066</v>
+        <v>352027</v>
       </c>
       <c r="R6" t="n">
-        <v>6422381</v>
+        <v>6422353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,22 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,15 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114560405</v>
+        <v>114560409</v>
       </c>
       <c r="B7" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352088</v>
+        <v>352045</v>
       </c>
       <c r="R7" t="n">
-        <v>6422365</v>
+        <v>6422373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,15 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114563379</v>
+        <v>114560410</v>
       </c>
       <c r="B8" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1424,14 +1354,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>detektor med höghastighetsinspelning</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1440,13 +1365,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>352145</v>
+        <v>352083</v>
       </c>
       <c r="R8" t="n">
-        <v>6422465</v>
+        <v>6422350</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,12 +1395,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,15 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114560409</v>
+        <v>114560411</v>
       </c>
       <c r="B9" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>352045</v>
+        <v>352079</v>
       </c>
       <c r="R9" t="n">
-        <v>6422373</v>
+        <v>6422365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,12 +1501,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,15 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114560412</v>
+        <v>114560349</v>
       </c>
       <c r="B10" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,16 +1544,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1648,12 +1563,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1662,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>352091</v>
+        <v>352061</v>
       </c>
       <c r="R10" t="n">
-        <v>6422455</v>
+        <v>6422449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,12 +1607,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,37 +1639,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114560489</v>
+        <v>114560350</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1764,7 +1674,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1773,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>352096</v>
+        <v>352009</v>
       </c>
       <c r="R11" t="n">
-        <v>6422425</v>
+        <v>6422291</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114560411</v>
+        <v>114560352</v>
       </c>
       <c r="B12" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1884,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>352079</v>
+        <v>352051</v>
       </c>
       <c r="R12" t="n">
-        <v>6422365</v>
+        <v>6422382</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,12 +1819,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,37 +1851,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114563208</v>
+        <v>114560356</v>
       </c>
       <c r="B13" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1984,14 +1884,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2000,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>352058</v>
+        <v>352070</v>
       </c>
       <c r="R13" t="n">
-        <v>6422365</v>
+        <v>6422435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,22 +1925,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,37 +1957,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114563360</v>
+        <v>114560357</v>
       </c>
       <c r="B14" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2110,14 +1990,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>detektor med höghastighetsinspelning</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2126,13 +2001,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>352094</v>
+        <v>352055</v>
       </c>
       <c r="R14" t="n">
-        <v>6422418</v>
+        <v>6422379</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,47 +2063,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114560406</v>
+        <v>114560358</v>
       </c>
       <c r="B15" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2237,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>352027</v>
+        <v>352031</v>
       </c>
       <c r="R15" t="n">
-        <v>6422353</v>
+        <v>6422314</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2267,12 +2137,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,42 +2169,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114560488</v>
+        <v>114560412</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2343,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>352075</v>
+        <v>352091</v>
       </c>
       <c r="R16" t="n">
-        <v>6422382</v>
+        <v>6422455</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,12 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,47 +2275,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114560410</v>
+        <v>114563197</v>
       </c>
       <c r="B17" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103012</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2454,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>352083</v>
+        <v>352066</v>
       </c>
       <c r="R17" t="n">
-        <v>6422350</v>
+        <v>6422381</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,12 +2354,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-07-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,52 +2396,47 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114563361</v>
+        <v>114563201</v>
       </c>
       <c r="B18" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>detektor med höghastighetsinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2570,13 +2445,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>352029</v>
+        <v>352058</v>
       </c>
       <c r="R18" t="n">
-        <v>6422295</v>
+        <v>6422365</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,9 +2478,19 @@
           <t>2023-07-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,37 +2517,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114560352</v>
+        <v>114563208</v>
       </c>
       <c r="B19" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>205998</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2670,9 +2550,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2681,10 +2566,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>352051</v>
+        <v>352058</v>
       </c>
       <c r="R19" t="n">
-        <v>6422382</v>
+        <v>6422365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,12 +2596,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,6 +2635,339 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114563360</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>352094</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6422418</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114563361</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>352029</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6422295</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114563379</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>352145</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6422465</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57763-2024 artfynd.xlsx
+++ b/artfynd/A 57763-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114563174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560406</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560409</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560410</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560411</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560349</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560350</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560352</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560356</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560357</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560358</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560412</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114563197</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114563201</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2635,6 +2725,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114563208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2746,6 +2841,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114563360</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2857,6 +2957,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114563361</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2968,8 +3073,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114563379</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>